--- a/inventories/baseline/lci-Silver-Peak.xlsx
+++ b/inventories/baseline/lci-Silver-Peak.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/baseline/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0A3E487C9C2E5510D92B37EBDD1623646A7C03BD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{204DC581-E8E1-4AC1-9926-7C56C359AA8D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Silver Peak" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -220,8 +226,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,13 +273,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -311,7 +325,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -345,6 +359,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -379,9 +394,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -554,11 +570,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F264"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="47.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -574,7 +593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -582,7 +601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -590,7 +609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -598,7 +617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -606,7 +625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -614,7 +633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -622,12 +641,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -647,12 +666,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.00025</v>
+        <v>2.5000000000000001E-4</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -664,12 +683,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.00125</v>
+        <v>1.25E-3</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -681,7 +700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -698,12 +717,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>0.007206</v>
+        <v>7.2059999999999997E-3</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -715,7 +734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -723,7 +742,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -731,7 +750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -739,7 +758,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -747,7 +766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -755,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -763,7 +782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -771,12 +790,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -796,12 +815,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-0.1701336122745861</v>
+        <v>-0.17013361227458609</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -813,7 +832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -830,12 +849,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28">
-        <v>2.306639472870272</v>
+        <v>2.3066394728702719</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -847,12 +866,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29">
-        <v>0.4835069547134599</v>
+        <v>0.48350695471345989</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -864,7 +883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>2</v>
       </c>
@@ -872,7 +891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -880,7 +899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -888,7 +907,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -896,7 +915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -904,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -912,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -920,12 +939,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -945,7 +964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -962,12 +981,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
       <c r="B41">
-        <v>0.4503216190919153</v>
+        <v>0.45032161909191532</v>
       </c>
       <c r="C41" t="s">
         <v>1</v>
@@ -979,12 +998,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>32</v>
       </c>
       <c r="B42">
-        <v>0.4370979761351059</v>
+        <v>0.43709797613510593</v>
       </c>
       <c r="C42" t="s">
         <v>1</v>
@@ -996,7 +1015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>30</v>
       </c>
@@ -1013,7 +1032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -1030,7 +1049,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>2</v>
       </c>
@@ -1038,7 +1057,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1046,7 +1065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1054,7 +1073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1062,7 +1081,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1070,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -1078,7 +1097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -1086,12 +1105,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -1128,12 +1147,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>26</v>
       </c>
       <c r="B56">
-        <v>5.692041315476785</v>
+        <v>5.6920413154767848</v>
       </c>
       <c r="C56" t="s">
         <v>1</v>
@@ -1145,12 +1164,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>22</v>
       </c>
       <c r="B57">
-        <v>0.006166378091766517</v>
+        <v>6.1663780917665173E-3</v>
       </c>
       <c r="C57" t="s">
         <v>23</v>
@@ -1162,12 +1181,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>36</v>
       </c>
       <c r="B58">
-        <v>-0.004692041315476785</v>
+        <v>-4.6920413154767854E-3</v>
       </c>
       <c r="C58" t="s">
         <v>1</v>
@@ -1179,7 +1198,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>2</v>
       </c>
@@ -1187,7 +1206,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -1203,7 +1222,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1211,7 +1230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -1219,7 +1238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -1227,7 +1246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -1235,12 +1254,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -1260,7 +1279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -1277,7 +1296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>38</v>
       </c>
@@ -1294,12 +1313,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>22</v>
       </c>
       <c r="B71">
-        <v>0.002527777777777778</v>
+        <v>2.5277777777777781E-3</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -1311,12 +1330,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>36</v>
       </c>
       <c r="B72">
-        <v>-0.001333333333333333</v>
+        <v>-1.3333333333333331E-3</v>
       </c>
       <c r="C72" t="s">
         <v>1</v>
@@ -1328,7 +1347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>2</v>
       </c>
@@ -1336,7 +1355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -1344,7 +1363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -1352,7 +1371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -1368,7 +1387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -1384,12 +1403,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>13</v>
       </c>
@@ -1409,7 +1428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>32</v>
       </c>
@@ -1426,7 +1445,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -1443,12 +1462,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>22</v>
       </c>
       <c r="B85">
-        <v>0.0005263157894736843</v>
+        <v>5.2631578947368431E-4</v>
       </c>
       <c r="C85" t="s">
         <v>23</v>
@@ -1460,12 +1479,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>40</v>
       </c>
       <c r="B86">
-        <v>-0.05263157894736843</v>
+        <v>-5.2631578947368432E-2</v>
       </c>
       <c r="C86" t="s">
         <v>41</v>
@@ -1477,7 +1496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>2</v>
       </c>
@@ -1485,7 +1504,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -1501,7 +1520,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1528,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -1517,7 +1536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>8</v>
       </c>
@@ -1525,7 +1544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -1533,12 +1552,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -1558,7 +1577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>42</v>
       </c>
@@ -1575,12 +1594,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>43</v>
       </c>
       <c r="B98">
-        <v>1.052631578947368</v>
+        <v>1.0526315789473679</v>
       </c>
       <c r="C98" t="s">
         <v>1</v>
@@ -1592,12 +1611,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>22</v>
       </c>
       <c r="B99">
-        <v>0.0005263157894736842</v>
+        <v>5.263157894736842E-4</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
@@ -1609,12 +1628,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
       <c r="B100">
-        <v>-0.05263157894736842</v>
+        <v>-5.2631578947368418E-2</v>
       </c>
       <c r="C100" t="s">
         <v>41</v>
@@ -1626,7 +1645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>2</v>
       </c>
@@ -1634,7 +1653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -1642,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -1650,7 +1669,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -1658,7 +1677,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -1666,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -1674,7 +1693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -1682,12 +1701,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -1707,7 +1726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>44</v>
       </c>
@@ -1724,7 +1743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>45</v>
       </c>
@@ -1741,12 +1760,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>22</v>
       </c>
       <c r="B113">
-        <v>0.002527777777777778</v>
+        <v>2.5277777777777781E-3</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
@@ -1758,12 +1777,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>36</v>
       </c>
       <c r="B114">
-        <v>-0.001333333333333333</v>
+        <v>-1.3333333333333331E-3</v>
       </c>
       <c r="C114" t="s">
         <v>1</v>
@@ -1775,7 +1794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>2</v>
       </c>
@@ -1783,7 +1802,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -1791,7 +1810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -1799,7 +1818,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -1807,7 +1826,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -1815,7 +1834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -1823,7 +1842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -1831,12 +1850,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -1856,7 +1875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>43</v>
       </c>
@@ -1873,12 +1892,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>3</v>
       </c>
       <c r="B126">
-        <v>0.9276437847866419</v>
+        <v>0.92764378478664189</v>
       </c>
       <c r="C126" t="s">
         <v>1</v>
@@ -1890,12 +1909,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>37</v>
       </c>
       <c r="B127">
-        <v>0.07235621521335807</v>
+        <v>7.2356215213358069E-2</v>
       </c>
       <c r="C127" t="s">
         <v>1</v>
@@ -1907,7 +1926,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -1924,7 +1943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>2</v>
       </c>
@@ -1932,7 +1951,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -1940,7 +1959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -1948,7 +1967,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -1956,7 +1975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -1964,7 +1983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -1972,7 +1991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -1980,12 +1999,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -2005,12 +2024,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>46</v>
       </c>
       <c r="B139">
-        <v>0.01158666695459362</v>
+        <v>1.158666695459362E-2</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
@@ -2022,12 +2041,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>47</v>
       </c>
       <c r="B140">
-        <v>5.324406555121015E-10</v>
+        <v>5.3244065551210152E-10</v>
       </c>
       <c r="D140" t="s">
         <v>48</v>
@@ -2039,7 +2058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>50</v>
       </c>
@@ -2056,7 +2075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>52</v>
       </c>
@@ -2073,7 +2092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -2090,7 +2109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>39</v>
       </c>
@@ -2107,12 +2126,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>3</v>
       </c>
       <c r="B145">
-        <v>0.170425617459418</v>
+        <v>0.17042561745941801</v>
       </c>
       <c r="C145" t="s">
         <v>1</v>
@@ -2124,12 +2143,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>53</v>
       </c>
       <c r="B146">
-        <v>0.000131839637996969</v>
+        <v>1.31839637996969E-4</v>
       </c>
       <c r="C146" t="s">
         <v>1</v>
@@ -2141,12 +2160,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>22</v>
       </c>
       <c r="B147">
-        <v>0.03656973811806428</v>
+        <v>3.6569738118064278E-2</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2158,12 +2177,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>55</v>
       </c>
       <c r="B148">
-        <v>0.04710856661306193</v>
+        <v>4.7108566613061932E-2</v>
       </c>
       <c r="C148" t="s">
         <v>41</v>
@@ -2175,12 +2194,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>56</v>
       </c>
       <c r="B149">
-        <v>0.000279526155479775</v>
+        <v>2.7952615547977499E-4</v>
       </c>
       <c r="C149" t="s">
         <v>41</v>
@@ -2192,12 +2211,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>57</v>
       </c>
       <c r="B150">
-        <v>-3.718705291323839E-16</v>
+        <v>-3.7187052913238388E-16</v>
       </c>
       <c r="C150" t="s">
         <v>41</v>
@@ -2209,12 +2228,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>36</v>
       </c>
       <c r="B151">
-        <v>-0.000155292308599875</v>
+        <v>-1.55292308599875E-4</v>
       </c>
       <c r="C151" t="s">
         <v>1</v>
@@ -2226,7 +2245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>2</v>
       </c>
@@ -2234,7 +2253,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -2242,7 +2261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -2250,7 +2269,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>6</v>
       </c>
@@ -2258,7 +2277,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>7</v>
       </c>
@@ -2266,7 +2285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -2274,7 +2293,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -2282,12 +2301,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -2307,12 +2326,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>59</v>
       </c>
       <c r="B162">
-        <v>-0.0006900000000000001</v>
+        <v>-6.9000000000000008E-4</v>
       </c>
       <c r="D162" t="s">
         <v>11</v>
@@ -2324,12 +2343,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>27</v>
       </c>
       <c r="B163">
-        <v>-0.004860000000000001</v>
+        <v>-4.8600000000000006E-3</v>
       </c>
       <c r="D163" t="s">
         <v>28</v>
@@ -2341,12 +2360,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>61</v>
       </c>
       <c r="B164">
-        <v>-0.00021</v>
+        <v>-2.1000000000000001E-4</v>
       </c>
       <c r="D164" t="s">
         <v>11</v>
@@ -2358,7 +2377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>58</v>
       </c>
@@ -2375,12 +2394,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>3</v>
       </c>
       <c r="B166">
-        <v>0.8250000000000001</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="C166" t="s">
         <v>1</v>
@@ -2392,7 +2411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>42</v>
       </c>
@@ -2409,12 +2428,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>22</v>
       </c>
       <c r="B168">
-        <v>0.00246</v>
+        <v>2.4599999999999999E-3</v>
       </c>
       <c r="C168" t="s">
         <v>23</v>
@@ -2426,12 +2445,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>62</v>
       </c>
       <c r="B169">
-        <v>0.00072</v>
+        <v>7.2000000000000005E-4</v>
       </c>
       <c r="C169" t="s">
         <v>41</v>
@@ -2443,12 +2462,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>63</v>
       </c>
       <c r="B170">
-        <v>0.00036</v>
+        <v>3.6000000000000002E-4</v>
       </c>
       <c r="C170" t="s">
         <v>34</v>
@@ -2460,7 +2479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>2</v>
       </c>
@@ -2468,7 +2487,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>4</v>
       </c>
@@ -2476,7 +2495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -2484,7 +2503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -2492,7 +2511,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -2500,7 +2519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>8</v>
       </c>
@@ -2508,7 +2527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -2516,12 +2535,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -2541,12 +2560,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>59</v>
       </c>
       <c r="B181">
-        <v>-0.0006900000000000001</v>
+        <v>-6.9000000000000008E-4</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
@@ -2558,12 +2577,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>27</v>
       </c>
       <c r="B182">
-        <v>-0.004860000000000001</v>
+        <v>-4.8600000000000006E-3</v>
       </c>
       <c r="D182" t="s">
         <v>28</v>
@@ -2575,12 +2594,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>61</v>
       </c>
       <c r="B183">
-        <v>-0.00021</v>
+        <v>-2.1000000000000001E-4</v>
       </c>
       <c r="D183" t="s">
         <v>11</v>
@@ -2592,7 +2611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>64</v>
       </c>
@@ -2609,12 +2628,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>3</v>
       </c>
       <c r="B185">
-        <v>0.8250000000000001</v>
+        <v>0.82500000000000007</v>
       </c>
       <c r="C185" t="s">
         <v>1</v>
@@ -2626,7 +2645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>58</v>
       </c>
@@ -2643,12 +2662,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>22</v>
       </c>
       <c r="B187">
-        <v>0.00246</v>
+        <v>2.4599999999999999E-3</v>
       </c>
       <c r="C187" t="s">
         <v>23</v>
@@ -2660,12 +2679,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>62</v>
       </c>
       <c r="B188">
-        <v>0.00072</v>
+        <v>7.2000000000000005E-4</v>
       </c>
       <c r="C188" t="s">
         <v>41</v>
@@ -2677,12 +2696,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>63</v>
       </c>
       <c r="B189">
-        <v>0.00036</v>
+        <v>3.6000000000000002E-4</v>
       </c>
       <c r="C189" t="s">
         <v>34</v>
@@ -2694,7 +2713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>2</v>
       </c>
@@ -2702,7 +2721,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -2710,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -2718,7 +2737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -2726,7 +2745,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>7</v>
       </c>
@@ -2734,7 +2753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>8</v>
       </c>
@@ -2742,7 +2761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -2750,12 +2769,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -2775,12 +2794,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>59</v>
       </c>
       <c r="B200">
-        <v>-0.00023</v>
+        <v>-2.3000000000000001E-4</v>
       </c>
       <c r="D200" t="s">
         <v>11</v>
@@ -2792,12 +2811,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>27</v>
       </c>
       <c r="B201">
-        <v>-0.00162</v>
+        <v>-1.6199999999999999E-3</v>
       </c>
       <c r="D201" t="s">
         <v>28</v>
@@ -2809,12 +2828,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>61</v>
       </c>
       <c r="B202">
-        <v>-7.000000000000001E-05</v>
+        <v>-7.0000000000000007E-5</v>
       </c>
       <c r="D202" t="s">
         <v>11</v>
@@ -2826,7 +2845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>29</v>
       </c>
@@ -2843,12 +2862,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>3</v>
       </c>
       <c r="B204">
-        <v>0.1375</v>
+        <v>0.13750000000000001</v>
       </c>
       <c r="C204" t="s">
         <v>1</v>
@@ -2860,7 +2879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>64</v>
       </c>
@@ -2877,12 +2896,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>22</v>
       </c>
       <c r="B206">
-        <v>0.00082</v>
+        <v>8.1999999999999998E-4</v>
       </c>
       <c r="C206" t="s">
         <v>23</v>
@@ -2894,12 +2913,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>62</v>
       </c>
       <c r="B207">
-        <v>0.00024</v>
+        <v>2.4000000000000001E-4</v>
       </c>
       <c r="C207" t="s">
         <v>41</v>
@@ -2911,12 +2930,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>63</v>
       </c>
       <c r="B208">
-        <v>0.00012</v>
+        <v>1.2E-4</v>
       </c>
       <c r="C208" t="s">
         <v>34</v>
@@ -2928,7 +2947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>2</v>
       </c>
@@ -2936,7 +2955,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>4</v>
       </c>
@@ -2944,7 +2963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -2952,7 +2971,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -2960,7 +2979,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>7</v>
       </c>
@@ -2968,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>8</v>
       </c>
@@ -2976,7 +2995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -2984,12 +3003,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>13</v>
       </c>
@@ -3009,7 +3028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>27</v>
       </c>
@@ -3026,7 +3045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>65</v>
       </c>
@@ -3043,7 +3062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>44</v>
       </c>
@@ -3060,12 +3079,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>30</v>
       </c>
       <c r="B222">
-        <v>0.3529411764705883</v>
+        <v>0.35294117647058831</v>
       </c>
       <c r="C222" t="s">
         <v>1</v>
@@ -3077,7 +3096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>22</v>
       </c>
@@ -3094,7 +3113,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>2</v>
       </c>
@@ -3102,7 +3121,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>4</v>
       </c>
@@ -3110,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -3118,7 +3137,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -3126,7 +3145,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>7</v>
       </c>
@@ -3134,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>8</v>
       </c>
@@ -3142,7 +3161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -3150,12 +3169,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>13</v>
       </c>
@@ -3175,7 +3194,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>45</v>
       </c>
@@ -3192,7 +3211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>3</v>
       </c>
@@ -3209,12 +3228,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>35</v>
       </c>
       <c r="B236">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="C236" t="s">
         <v>1</v>
@@ -3226,7 +3245,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>30</v>
       </c>
@@ -3243,7 +3262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>2</v>
       </c>
@@ -3251,7 +3270,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>4</v>
       </c>
@@ -3259,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -3267,7 +3286,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -3275,7 +3294,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>7</v>
       </c>
@@ -3283,7 +3302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>8</v>
       </c>
@@ -3291,7 +3310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -3299,12 +3318,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>13</v>
       </c>
@@ -3324,7 +3343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>38</v>
       </c>
@@ -3341,7 +3360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>3</v>
       </c>
@@ -3358,12 +3377,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>31</v>
       </c>
       <c r="B250">
-        <v>4.732550838598574</v>
+        <v>4.7325508385985744</v>
       </c>
       <c r="C250" t="s">
         <v>1</v>
@@ -3375,7 +3394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>30</v>
       </c>
@@ -3392,7 +3411,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>2</v>
       </c>
@@ -3400,7 +3419,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>4</v>
       </c>
@@ -3408,7 +3427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -3416,7 +3435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -3424,7 +3443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>7</v>
       </c>
@@ -3432,7 +3451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>8</v>
       </c>
@@ -3440,7 +3459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -3448,12 +3467,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>13</v>
       </c>
@@ -3473,7 +3492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>15</v>
       </c>
@@ -3490,7 +3509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>36</v>
       </c>
@@ -3507,7 +3526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>66</v>
       </c>
@@ -3527,4 +3546,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d465f887-04a9-4c17-8b62-103eddccf68b}" enabled="1" method="Standard" siteId="{ca2a7f76-dbd7-4ec0-9108-6b3d524fb7c8}" removed="0"/>
+</clbl:labelList>
 </file>